--- a/daily_matches/job_matches_2026-06-21.xlsx
+++ b/daily_matches/job_matches_2026-06-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full Stack Java Technical Specialist - React.js</t>
+          <t>Software Engineer - AI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Ingram Micro</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, Docker, Kubernetes</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Pinecone, ChromaDB, Prompt Engineering, spaCy, NLTK, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,59 +496,59 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86a514b2ddb169b4</t>
+          <t>https://www.indeed.com/viewjob?jk=da688748068d58e3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fresh Food QA Technician</t>
+          <t>Microsoft Fabric Engineer | Camden Corporate Office</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Camden Property Trust</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kinesis, Docker, Kubernetes, CI/CD, Terraform, MongoDB, NoSQL</t>
+          <t>Copilot, Synapse, Dataflow, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4195bab3d9303fad</t>
+          <t>https://www.indeed.com/viewjob?jk=6fe0c8f580c4042e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Scientist II - Children's Learning Institute</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nestlé USA</t>
+          <t>UTHealth Houston</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,52 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Azure ML, Snowflake, Databricks, Tableau, Power BI, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, Git, Hadoop, Tableau, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c691fdca5525a7a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Specialist - Data Engineering</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>LTIMindtree</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, Databricks, PySpark, Hadoop, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a4405fe7120dba5a</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2251d42e71aa1b</t>
         </is>
       </c>
     </row>
